--- a/output/graficos_regionales_salud/plot_s_isapre_a_2024_nuble.xlsx
+++ b/output/graficos_regionales_salud/plot_s_isapre_a_2024_nuble.xlsx
@@ -10,6 +10,7 @@
     <sheet name="global" sheetId="1" r:id="rId1"/>
     <sheet name="edades" sheetId="2" r:id="rId2"/>
     <sheet name="historico" sheetId="3" r:id="rId3"/>
+    <sheet name="grupo_moda" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -383,7 +384,7 @@
         <v>4.414907729497082</v>
       </c>
       <c r="C2">
-        <v>11.71443611727853</v>
+        <v>11.9314447005561</v>
       </c>
     </row>
     <row r="3">
@@ -396,7 +397,7 @@
         <v>6.324560031435864</v>
       </c>
       <c r="C3">
-        <v>14.40432258615322</v>
+        <v>14.67033142805598</v>
       </c>
     </row>
     <row r="4">
@@ -446,10 +447,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>5.737239793327958</v>
+        <v>4.521489431812832</v>
       </c>
       <c r="C2">
-        <v>12.48629652212012</v>
+        <v>12.87796578676103</v>
       </c>
     </row>
     <row r="3">
@@ -462,7 +463,7 @@
         <v>4.500981339895128</v>
       </c>
       <c r="C3">
-        <v>11.78102217815983</v>
+        <v>11.9270536513881</v>
       </c>
     </row>
     <row r="4">
@@ -475,7 +476,7 @@
         <v>5.404977226219552</v>
       </c>
       <c r="C4">
-        <v>13.13143478377702</v>
+        <v>13.30552607709379</v>
       </c>
     </row>
     <row r="5">
@@ -488,7 +489,7 @@
         <v>8.944497477158052</v>
       </c>
       <c r="C5">
-        <v>17.85887356906912</v>
+        <v>18.12074296681788</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +502,7 @@
         <v>6.68327106683271</v>
       </c>
       <c r="C6">
-        <v>15.74321024003533</v>
+        <v>15.97837728982048</v>
       </c>
     </row>
     <row r="7">
@@ -514,7 +515,7 @@
         <v>4.902097706767967</v>
       </c>
       <c r="C7">
-        <v>11.49764061159679</v>
+        <v>11.66609085271251</v>
       </c>
     </row>
     <row r="8">
@@ -527,7 +528,7 @@
         <v>3.134439824774559</v>
       </c>
       <c r="C8">
-        <v>8.687421205158572</v>
+        <v>8.906808400068124</v>
       </c>
     </row>
   </sheetData>
@@ -664,4 +665,15 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/output/graficos_regionales_salud/plot_s_isapre_a_2024_nuble.xlsx
+++ b/output/graficos_regionales_salud/plot_s_isapre_a_2024_nuble.xlsx
@@ -447,10 +447,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>4.521489431812832</v>
+        <v>5.737239793327958</v>
       </c>
       <c r="C2">
-        <v>12.87796578676103</v>
+        <v>12.48629652212012</v>
       </c>
     </row>
     <row r="3">
@@ -463,7 +463,7 @@
         <v>4.500981339895128</v>
       </c>
       <c r="C3">
-        <v>11.9270536513881</v>
+        <v>11.78102217815983</v>
       </c>
     </row>
     <row r="4">
@@ -476,7 +476,7 @@
         <v>5.404977226219552</v>
       </c>
       <c r="C4">
-        <v>13.30552607709379</v>
+        <v>13.13143478377702</v>
       </c>
     </row>
     <row r="5">
@@ -489,7 +489,7 @@
         <v>8.944497477158052</v>
       </c>
       <c r="C5">
-        <v>18.12074296681788</v>
+        <v>17.85887356906912</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         <v>6.68327106683271</v>
       </c>
       <c r="C6">
-        <v>15.97837728982048</v>
+        <v>15.74321024003533</v>
       </c>
     </row>
     <row r="7">
@@ -515,7 +515,7 @@
         <v>4.902097706767967</v>
       </c>
       <c r="C7">
-        <v>11.66609085271251</v>
+        <v>11.49764061159679</v>
       </c>
     </row>
     <row r="8">
@@ -528,7 +528,7 @@
         <v>3.134439824774559</v>
       </c>
       <c r="C8">
-        <v>8.906808400068124</v>
+        <v>8.687421205158572</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_salud/plot_s_isapre_a_2024_nuble.xlsx
+++ b/output/graficos_regionales_salud/plot_s_isapre_a_2024_nuble.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -365,10 +365,15 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>raw_region</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>tasa_neta</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>nacional</t>
         </is>
@@ -381,9 +386,12 @@
         </is>
       </c>
       <c r="B2">
+        <v>11981</v>
+      </c>
+      <c r="C2">
         <v>4.414907729497082</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>11.9314447005561</v>
       </c>
     </row>
@@ -394,9 +402,12 @@
         </is>
       </c>
       <c r="B3">
+        <v>16578</v>
+      </c>
+      <c r="C3">
         <v>6.324560031435864</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>14.67033142805598</v>
       </c>
     </row>
@@ -407,9 +418,12 @@
         </is>
       </c>
       <c r="B4">
+        <v>28559</v>
+      </c>
+      <c r="C4">
         <v>5.353169746034186</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>13.04448320317316</v>
       </c>
     </row>

--- a/output/graficos_regionales_salud/plot_s_isapre_a_2024_nuble.xlsx
+++ b/output/graficos_regionales_salud/plot_s_isapre_a_2024_nuble.xlsx
@@ -10,7 +10,6 @@
     <sheet name="global" sheetId="1" r:id="rId1"/>
     <sheet name="edades" sheetId="2" r:id="rId2"/>
     <sheet name="historico" sheetId="3" r:id="rId3"/>
-    <sheet name="grupo_moda" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -679,15 +678,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1"/>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/output/graficos_regionales_salud/plot_s_isapre_a_2024_nuble.xlsx
+++ b/output/graficos_regionales_salud/plot_s_isapre_a_2024_nuble.xlsx
@@ -1,48 +1,154 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="global" sheetId="1" r:id="rId1"/>
-    <sheet name="edades" sheetId="2" r:id="rId2"/>
-    <sheet name="historico" sheetId="3" r:id="rId3"/>
+    <sheet name="Global" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Edades" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Histórico" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Histórico'!$A$1:$C$9</definedName>
+  </definedNames>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+  <si>
+    <t xml:space="preserve">Categoría</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Media nacional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hombres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mujeres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fecha de creación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27 21:29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIT - MDSF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imagen asociada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">plot_s_isapre_a_2024_nuble.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicador</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Unidad territorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tramo de edad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor regional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor nacional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hasta 14 años</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 a 24 años</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 a 34 años</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35 a 44 años</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45 a 54 años</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55 a 64 años</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desde 65 años</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Serie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nacional</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
       <b/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00135A"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,21 +156,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
 
@@ -114,10 +236,6 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -143,15 +261,12 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -177,6 +292,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -352,330 +468,354 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="11.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="16.71" hidden="0" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>indicador</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>raw_region</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>tasa_neta</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>nacional</t>
-        </is>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Mujeres</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>11981</v>
-      </c>
-      <c r="C2">
-        <v>4.414907729497082</v>
-      </c>
-      <c r="D2">
-        <v>11.9314447005561</v>
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>7.34</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Hombres</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>16578</v>
-      </c>
-      <c r="C3">
-        <v>6.324560031435864</v>
-      </c>
-      <c r="D3">
-        <v>14.67033142805598</v>
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>5.97</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>28559</v>
-      </c>
-      <c r="C4">
-        <v>5.353169746034186</v>
-      </c>
-      <c r="D4">
-        <v>13.04448320317316</v>
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>13.04</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="24.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="60.71" hidden="0" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>subgroup</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>value_region</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>value_national</t>
-        </is>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Hasta 14 años</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>5.737239793327958</v>
-      </c>
-      <c r="C2">
-        <v>12.48629652212012</v>
+      <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>15 a 24 años</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>4.500981339895128</v>
-      </c>
-      <c r="C3">
-        <v>11.78102217815983</v>
+      <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>25 a 34 años</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>5.404977226219552</v>
-      </c>
-      <c r="C4">
-        <v>13.13143478377702</v>
+      <c r="A4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>35 a 44 años</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>8.944497477158052</v>
-      </c>
-      <c r="C5">
-        <v>17.85887356906912</v>
+      <c r="A5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>45 a 54 años</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>6.68327106683271</v>
-      </c>
-      <c r="C6">
-        <v>15.74321024003533</v>
+      <c r="A6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>55 a 64 años</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>4.902097706767967</v>
-      </c>
-      <c r="C7">
-        <v>11.49764061159679</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Desde 65 años</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>3.134439824774559</v>
-      </c>
-      <c r="C8">
-        <v>8.687421205158572</v>
+      <c r="A7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="15.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="16.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="16.71" hidden="0" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>year</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>serie</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
+      <c r="A2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>12.49</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>11.78</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>13.13</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>8.94</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>17.86</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>15.74</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>8.69</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C8"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="10.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Región</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>7.416197341511182</v>
+      <c r="B2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>7.42</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
+      <c r="A3" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="C3">
-        <v>16.30020507167294</v>
+      <c r="B3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>16.3</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
+      <c r="A4" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Región</t>
-        </is>
-      </c>
-      <c r="C4">
-        <v>7.046979865771812</v>
+      <c r="B4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>7.05</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
+      <c r="A5" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>16.05871113116685</v>
+      <c r="B5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>16.06</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
+      <c r="A6" s="2" t="n">
         <v>2023</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Región</t>
-        </is>
-      </c>
-      <c r="C6">
-        <v>5.955434903843064</v>
+      <c r="B6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>5.96</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
+      <c r="A7" s="2" t="n">
         <v>2023</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>14.11079873781682</v>
+      <c r="B7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>14.11</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
+      <c r="A8" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Región</t>
-        </is>
-      </c>
-      <c r="C8">
-        <v>5.353169746034186</v>
+      <c r="B8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>5.35</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
+      <c r="A9" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>13.04448320317316</v>
+      <c r="B9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>13.04</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C9"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
--- a/output/graficos_regionales_salud/plot_s_isapre_a_2024_nuble.xlsx
+++ b/output/graficos_regionales_salud/plot_s_isapre_a_2024_nuble.xlsx
@@ -6,36 +6,77 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Global" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Regional" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Edades" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Histórico" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Histórico" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Histórico'!$A$1:$C$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Histórico'!$A$1:$C$9</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
-  <si>
-    <t xml:space="preserve">Categoría</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+  <si>
+    <t xml:space="preserve">Región</t>
   </si>
   <si>
     <t xml:space="preserve">Valor</t>
   </si>
   <si>
+    <t xml:space="preserve">Ranking</t>
+  </si>
+  <si>
     <t xml:space="preserve">Media nacional</t>
   </si>
   <si>
-    <t xml:space="preserve">Hombres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mujeres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total</t>
+    <t xml:space="preserve">Metropolitana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antofagasta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magallanes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valparaíso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atacama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O'Higgins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tarapacá</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Lagos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biobío</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coquimbo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Ríos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arica y Parinacota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aysén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Araucanía</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ñuble</t>
   </si>
   <si>
     <t xml:space="preserve">Campo</t>
@@ -44,7 +85,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 21:29</t>
+    <t xml:space="preserve">2026-07-30 10:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -69,36 +110,6 @@
   </si>
   <si>
     <t xml:space="preserve">Año</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tramo de edad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor regional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor nacional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hasta 14 años</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 a 24 años</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 a 34 años</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35 a 44 años</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45 a 54 años</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55 a 64 años</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desde 65 años</t>
   </si>
   <si>
     <t xml:space="preserve">Serie</t>
@@ -472,9 +483,10 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="11.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="20.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="16.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="16.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -487,42 +499,236 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>3.16</v>
+        <v>20.15</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>7.34</v>
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>13.04</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>2.21</v>
+        <v>17.74</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>5.97</v>
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>13.04</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>11.64</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>13.04</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>13.04</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="C6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="D6" s="2" t="n">
+        <v>13.04</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>9.64</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>13.04</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>13.04</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>13.04</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>8.55</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>13.04</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>13.04</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>13.04</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>13.04</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>13.04</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>13.04</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>13.04</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="2" t="n">
         <v>5.35</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D17" s="2" t="n">
         <v>13.04</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C4"/>
+  <autoFilter ref="A1:D17"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -539,7 +745,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -547,50 +753,50 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -604,111 +810,6 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="15.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="16.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="16.71" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>5.74</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>12.49</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>11.78</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>13.13</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>8.94</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>17.86</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>6.68</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>15.74</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>8.69</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:C8"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
     <col min="1" max="1" width="10.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
@@ -716,10 +817,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -730,7 +831,7 @@
         <v>2021</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>7.42</v>
@@ -741,7 +842,7 @@
         <v>2021</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>16.3</v>
@@ -752,7 +853,7 @@
         <v>2022</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>7.05</v>
@@ -763,7 +864,7 @@
         <v>2022</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>16.06</v>
@@ -774,7 +875,7 @@
         <v>2023</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>5.96</v>
@@ -785,7 +886,7 @@
         <v>2023</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>14.11</v>
@@ -796,7 +897,7 @@
         <v>2024</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>5.35</v>
@@ -807,7 +908,7 @@
         <v>2024</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>13.04</v>

--- a/output/graficos_regionales_salud/plot_s_isapre_a_2024_nuble.xlsx
+++ b/output/graficos_regionales_salud/plot_s_isapre_a_2024_nuble.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t xml:space="preserve">Región</t>
   </si>
@@ -85,7 +85,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 10:56</t>
+    <t xml:space="preserve">2026-08-19 14:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -113,9 +113,6 @@
   </si>
   <si>
     <t xml:space="preserve">Serie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Region</t>
   </si>
   <si>
     <t xml:space="preserve">Nacional</t>
@@ -831,7 +828,7 @@
         <v>2021</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>7.42</v>
@@ -842,7 +839,7 @@
         <v>2021</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>16.3</v>
@@ -853,7 +850,7 @@
         <v>2022</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>7.05</v>
@@ -864,7 +861,7 @@
         <v>2022</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>16.06</v>
@@ -875,7 +872,7 @@
         <v>2023</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>5.96</v>
@@ -886,7 +883,7 @@
         <v>2023</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>14.11</v>
@@ -897,7 +894,7 @@
         <v>2024</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>5.35</v>
@@ -908,7 +905,7 @@
         <v>2024</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>13.04</v>

--- a/output/graficos_regionales_salud/plot_s_isapre_a_2024_nuble.xlsx
+++ b/output/graficos_regionales_salud/plot_s_isapre_a_2024_nuble.xlsx
@@ -85,7 +85,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 14:33</t>
+    <t xml:space="preserve">2026-08-28 15:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_salud/plot_s_isapre_a_2024_nuble.xlsx
+++ b/output/graficos_regionales_salud/plot_s_isapre_a_2024_nuble.xlsx
@@ -85,7 +85,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 15:05</t>
+    <t xml:space="preserve">2026-08-29 05:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_salud/plot_s_isapre_a_2024_nuble.xlsx
+++ b/output/graficos_regionales_salud/plot_s_isapre_a_2024_nuble.xlsx
@@ -85,7 +85,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-29 05:42</t>
+    <t xml:space="preserve">2026-09-06 18:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
